--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N82_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N82_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.67644098837233</v>
+        <v>9.534921660610504</v>
       </c>
       <c r="D2" t="n">
-        <v>57.94985281449287</v>
+        <v>9.416851082355091</v>
       </c>
       <c r="E2" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F2" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>81.26222282007448</v>
+        <v>13.2051112082621</v>
       </c>
       <c r="D3" t="n">
-        <v>80.59536576364577</v>
+        <v>13.09674693659244</v>
       </c>
       <c r="E3" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F3" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>63.11602915341454</v>
+        <v>10.25635473742986</v>
       </c>
       <c r="D4" t="n">
-        <v>62.4414833852922</v>
+        <v>10.14674105010998</v>
       </c>
       <c r="E4" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F4" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>71.56143270191559</v>
+        <v>11.62873281406128</v>
       </c>
       <c r="D5" t="n">
-        <v>69.59158429738314</v>
+        <v>11.30863244832476</v>
       </c>
       <c r="E5" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F5" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.71940538658743</v>
+        <v>7.266903375320457</v>
       </c>
       <c r="D6" t="n">
-        <v>42.72447427499493</v>
+        <v>6.942727069686676</v>
       </c>
       <c r="E6" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F6" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.88469631489808</v>
+        <v>4.693763151170938</v>
       </c>
       <c r="D7" t="n">
-        <v>29.36868828047409</v>
+        <v>4.772411845577039</v>
       </c>
       <c r="E7" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F7" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.31592600425237</v>
+        <v>6.71383797569101</v>
       </c>
       <c r="D8" t="n">
-        <v>40.1189944013649</v>
+        <v>6.519336590221797</v>
       </c>
       <c r="E8" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F8" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>50.74771329183399</v>
+        <v>8.246503409923024</v>
       </c>
       <c r="D9" t="n">
-        <v>49.84796903485687</v>
+        <v>8.100294968164242</v>
       </c>
       <c r="E9" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F9" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>50.98585304036249</v>
+        <v>8.285201119058904</v>
       </c>
       <c r="D10" t="n">
-        <v>51.41431651437284</v>
+        <v>8.354826433585586</v>
       </c>
       <c r="E10" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F10" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.06164806777731</v>
+        <v>3.585017811013812</v>
       </c>
       <c r="D11" t="n">
-        <v>22.4702557239922</v>
+        <v>3.651416555148733</v>
       </c>
       <c r="E11" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F11" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>23.82695344841143</v>
+        <v>3.871879935366858</v>
       </c>
       <c r="D12" t="n">
-        <v>25.46013962638422</v>
+        <v>4.137272689287436</v>
       </c>
       <c r="E12" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F12" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>51.81829622955048</v>
+        <v>8.420473137301954</v>
       </c>
       <c r="D13" t="n">
-        <v>53.07196252652518</v>
+        <v>8.624193910560342</v>
       </c>
       <c r="E13" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F13" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>40.87421845291313</v>
+        <v>6.642060498598385</v>
       </c>
       <c r="D14" t="n">
-        <v>42.88809807590149</v>
+        <v>6.969315937333993</v>
       </c>
       <c r="E14" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F14" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>54.80790275750593</v>
+        <v>8.906284198094713</v>
       </c>
       <c r="D15" t="n">
-        <v>56.45436007753516</v>
+        <v>9.173833512599463</v>
       </c>
       <c r="E15" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F15" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>55.03540595264077</v>
+        <v>8.943253467304126</v>
       </c>
       <c r="D16" t="n">
-        <v>56.87779676056972</v>
+        <v>9.24264197359258</v>
       </c>
       <c r="E16" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F16" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>59.79421369846137</v>
+        <v>9.716559725999973</v>
       </c>
       <c r="D17" t="n">
-        <v>61.54084423357867</v>
+        <v>10.00038718795654</v>
       </c>
       <c r="E17" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F17" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>53.84071695314965</v>
+        <v>8.749116504886819</v>
       </c>
       <c r="D18" t="n">
-        <v>55.79882327915933</v>
+        <v>9.067308782863391</v>
       </c>
       <c r="E18" t="n">
-        <v>15.24482682891027</v>
+        <v>2.477284359697919</v>
       </c>
       <c r="F18" t="n">
-        <v>14.92660750274285</v>
+        <v>2.425573719195712</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
